--- a/examples/stm32/f4/f446/i2c signal.xlsx
+++ b/examples/stm32/f4/f446/i2c signal.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dcmvd\Documents\GitHub\libopencm3-examples\examples\stm32\f4\f446\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC6F00D5-0D0E-4650-876A-99FC1DD15535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D14651D5-7A54-4D08-9560-EEA52DA3F8E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2A5A3464-893F-43D8-8F1A-EA42950CCA41}"/>
   </bookViews>
@@ -280,15 +280,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -297,16 +303,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -326,9 +322,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -366,7 +362,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -472,7 +468,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -614,7 +610,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -886,9 +882,9 @@
       </c>
     </row>
     <row r="5" spans="10:94" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J5" s="11"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
       <c r="O5" s="1"/>
@@ -969,441 +965,359 @@
       <c r="CL5" s="4"/>
       <c r="CM5" s="1"/>
       <c r="CN5" s="2"/>
-      <c r="CO5" s="12"/>
-      <c r="CP5" s="11"/>
+      <c r="CO5" s="8"/>
+      <c r="CP5" s="7"/>
     </row>
-    <row r="6" spans="10:94" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="6"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="6"/>
-      <c r="AB6" s="6"/>
-      <c r="AC6" s="6"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="6"/>
-      <c r="AO6" s="6"/>
-      <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-      <c r="AR6" s="6"/>
-      <c r="AS6" s="6"/>
-      <c r="AT6" s="6"/>
-      <c r="AU6" s="6"/>
-      <c r="AV6" s="6"/>
-      <c r="AW6" s="6"/>
-      <c r="AX6" s="6"/>
-      <c r="AY6" s="6"/>
-      <c r="AZ6" s="6"/>
-      <c r="BA6" s="6"/>
-      <c r="BB6" s="6"/>
-      <c r="BC6" s="6"/>
-      <c r="BD6" s="6"/>
-      <c r="BE6" s="6"/>
-      <c r="BF6" s="6"/>
-      <c r="BG6" s="6"/>
-      <c r="BH6" s="6"/>
-      <c r="BI6" s="6"/>
-      <c r="BJ6" s="6"/>
-      <c r="BK6" s="6"/>
-      <c r="BL6" s="6"/>
-      <c r="BM6" s="6"/>
-      <c r="BN6" s="6"/>
-      <c r="BO6" s="6"/>
-      <c r="BP6" s="6"/>
-      <c r="BQ6" s="6"/>
-      <c r="BR6" s="6"/>
-      <c r="BS6" s="6"/>
-      <c r="BT6" s="6"/>
-      <c r="BU6" s="6"/>
-      <c r="BV6" s="6"/>
-      <c r="BW6" s="6"/>
-      <c r="BX6" s="6"/>
-      <c r="BY6" s="6"/>
-      <c r="BZ6" s="6"/>
-      <c r="CA6" s="6"/>
-      <c r="CB6" s="6"/>
-      <c r="CC6" s="6"/>
-      <c r="CD6" s="6"/>
-      <c r="CE6" s="6"/>
-      <c r="CF6" s="6"/>
-      <c r="CG6" s="6"/>
-      <c r="CH6" s="6"/>
-      <c r="CI6" s="6"/>
-      <c r="CJ6" s="6"/>
-      <c r="CK6" s="6"/>
-      <c r="CL6" s="6"/>
-      <c r="CM6" s="6"/>
-      <c r="CN6" s="6"/>
-      <c r="CO6" s="6"/>
-      <c r="CP6" s="6"/>
-    </row>
+    <row r="6" spans="10:94" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="10:94" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="J7" s="6"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="6"/>
       <c r="L7" s="3"/>
       <c r="M7" s="5"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="P7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="R7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="S7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="T7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="U7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="V7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="W7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="X7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AA7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AB7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AD7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AF7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AM7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AN7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AO7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="AP7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AQ7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AR7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AS7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AT7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="AU7" s="11"/>
-      <c r="AV7" s="7"/>
-      <c r="AW7" s="7"/>
-      <c r="AX7" s="7"/>
-      <c r="AY7" s="11"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="R7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="S7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="T7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="U7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="X7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AA7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AB7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AC7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AD7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="AU7" s="7"/>
+      <c r="AV7" s="6"/>
+      <c r="AW7" s="6"/>
+      <c r="AX7" s="6"/>
+      <c r="AY7" s="7"/>
       <c r="AZ7" s="3"/>
       <c r="BA7" s="4"/>
-      <c r="BB7" s="13"/>
-      <c r="BC7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BD7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BE7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BF7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BG7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BH7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BI7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BJ7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BK7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BL7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BM7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BN7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BO7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BP7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BQ7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BR7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BS7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BT7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BU7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BV7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="BW7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BX7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BY7" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="BZ7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CA7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CB7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CC7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CD7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CE7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CF7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CG7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CH7" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="CI7" s="11"/>
-      <c r="CJ7" s="7"/>
-      <c r="CK7" s="7"/>
-      <c r="CL7" s="7"/>
-      <c r="CM7" s="14"/>
+      <c r="BB7" s="9"/>
+      <c r="BC7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BD7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BE7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BF7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BG7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BH7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BI7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BJ7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BK7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BL7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BM7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BN7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BO7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BP7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BQ7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BR7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BS7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BT7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BU7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BV7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BW7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BX7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BY7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="BZ7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CA7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CB7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CC7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CD7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CE7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CF7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CG7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CH7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="CI7" s="7"/>
+      <c r="CJ7" s="6"/>
+      <c r="CK7" s="6"/>
+      <c r="CL7" s="6"/>
+      <c r="CM7" s="10"/>
       <c r="CN7" s="1"/>
       <c r="CO7" s="2"/>
-      <c r="CP7" s="7"/>
+      <c r="CP7" s="6"/>
     </row>
     <row r="9" spans="10:94" x14ac:dyDescent="0.25">
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="10"/>
-      <c r="AA9" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="10"/>
-      <c r="AE9" s="8" t="s">
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="14"/>
+      <c r="S9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="13"/>
+      <c r="U9" s="13"/>
+      <c r="V9" s="14"/>
+      <c r="W9" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="14"/>
+      <c r="AA9" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="14"/>
+      <c r="AE9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="AF9" s="9"/>
-      <c r="AG9" s="9"/>
-      <c r="AH9" s="10"/>
-      <c r="AI9" s="8" t="s">
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="14"/>
+      <c r="AI9" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="AJ9" s="9"/>
-      <c r="AK9" s="9"/>
-      <c r="AL9" s="10"/>
-      <c r="AM9" s="8" t="s">
+      <c r="AJ9" s="13"/>
+      <c r="AK9" s="13"/>
+      <c r="AL9" s="14"/>
+      <c r="AM9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="AN9" s="9"/>
-      <c r="AO9" s="9"/>
-      <c r="AP9" s="10"/>
-      <c r="AQ9" s="8" t="s">
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="14"/>
+      <c r="AQ9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="AR9" s="9"/>
-      <c r="AS9" s="9"/>
-      <c r="AT9" s="10"/>
-      <c r="AU9" s="8" t="s">
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="13"/>
+      <c r="AT9" s="14"/>
+      <c r="AU9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="AV9" s="9"/>
-      <c r="AW9" s="9"/>
-      <c r="AX9" s="10"/>
-      <c r="AY9" s="8" t="s">
+      <c r="AV9" s="13"/>
+      <c r="AW9" s="13"/>
+      <c r="AX9" s="14"/>
+      <c r="AY9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="AZ9" s="9"/>
-      <c r="BA9" s="9"/>
-      <c r="BB9" s="10"/>
-      <c r="BC9" s="8" t="s">
+      <c r="AZ9" s="13"/>
+      <c r="BA9" s="13"/>
+      <c r="BB9" s="14"/>
+      <c r="BC9" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="BD9" s="9"/>
-      <c r="BE9" s="9"/>
-      <c r="BF9" s="10"/>
-      <c r="BG9" s="8" t="s">
+      <c r="BD9" s="13"/>
+      <c r="BE9" s="13"/>
+      <c r="BF9" s="14"/>
+      <c r="BG9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="BH9" s="9"/>
-      <c r="BI9" s="9"/>
-      <c r="BJ9" s="10"/>
-      <c r="BK9" s="8" t="s">
+      <c r="BH9" s="13"/>
+      <c r="BI9" s="13"/>
+      <c r="BJ9" s="14"/>
+      <c r="BK9" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="BL9" s="9"/>
-      <c r="BM9" s="9"/>
-      <c r="BN9" s="10"/>
-      <c r="BO9" s="8" t="s">
+      <c r="BL9" s="13"/>
+      <c r="BM9" s="13"/>
+      <c r="BN9" s="14"/>
+      <c r="BO9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="BP9" s="9"/>
-      <c r="BQ9" s="9"/>
-      <c r="BR9" s="10"/>
-      <c r="BS9" s="8" t="s">
+      <c r="BP9" s="13"/>
+      <c r="BQ9" s="13"/>
+      <c r="BR9" s="14"/>
+      <c r="BS9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="BT9" s="9"/>
-      <c r="BU9" s="9"/>
-      <c r="BV9" s="10"/>
-      <c r="BW9" s="8" t="s">
+      <c r="BT9" s="13"/>
+      <c r="BU9" s="13"/>
+      <c r="BV9" s="14"/>
+      <c r="BW9" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="BX9" s="9"/>
-      <c r="BY9" s="9"/>
-      <c r="BZ9" s="10"/>
-      <c r="CA9" s="8" t="s">
+      <c r="BX9" s="13"/>
+      <c r="BY9" s="13"/>
+      <c r="BZ9" s="14"/>
+      <c r="CA9" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="CB9" s="9"/>
-      <c r="CC9" s="9"/>
-      <c r="CD9" s="10"/>
-      <c r="CE9" s="8" t="s">
+      <c r="CB9" s="13"/>
+      <c r="CC9" s="13"/>
+      <c r="CD9" s="14"/>
+      <c r="CE9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="CF9" s="9"/>
-      <c r="CG9" s="9"/>
-      <c r="CH9" s="10"/>
-      <c r="CI9" s="8" t="s">
+      <c r="CF9" s="13"/>
+      <c r="CG9" s="13"/>
+      <c r="CH9" s="14"/>
+      <c r="CI9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="CJ9" s="9"/>
-      <c r="CK9" s="9"/>
-      <c r="CL9" s="10"/>
-      <c r="CM9" s="8" t="s">
+      <c r="CJ9" s="13"/>
+      <c r="CK9" s="13"/>
+      <c r="CL9" s="14"/>
+      <c r="CM9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="CN9" s="9"/>
-      <c r="CO9" s="9"/>
-      <c r="CP9" s="10"/>
+      <c r="CN9" s="13"/>
+      <c r="CO9" s="13"/>
+      <c r="CP9" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="S9:V9"/>
+    <mergeCell ref="W9:Z9"/>
+    <mergeCell ref="AA9:AD9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="BK9:BN9"/>
     <mergeCell ref="BG9:BJ9"/>
     <mergeCell ref="AY9:BB9"/>
@@ -1419,11 +1333,6 @@
     <mergeCell ref="AQ9:AT9"/>
     <mergeCell ref="AU9:AX9"/>
     <mergeCell ref="BC9:BF9"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="S9:V9"/>
-    <mergeCell ref="W9:Z9"/>
-    <mergeCell ref="AA9:AD9"/>
-    <mergeCell ref="K9:N9"/>
     <mergeCell ref="AI9:AL9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
